--- a/Results_experiment/exp_4/eval_cycle_XII.xlsx
+++ b/Results_experiment/exp_4/eval_cycle_XII.xlsx
@@ -447,13 +447,13 @@
         <v>530</v>
       </c>
       <c r="D2">
-        <v>0.115302208700128</v>
+        <v>0.1763899039193928</v>
       </c>
       <c r="E2">
-        <v>7.629400060992866</v>
+        <v>7.361286959258614</v>
       </c>
       <c r="F2">
-        <v>5.634616354613934</v>
+        <v>5.684101148258965</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>509</v>
       </c>
       <c r="D3">
-        <v>0.5764461750930907</v>
+        <v>0.5767108677070003</v>
       </c>
       <c r="E3">
-        <v>4.079697310641092</v>
+        <v>4.078422343393508</v>
       </c>
       <c r="F3">
-        <v>2.753240897153707</v>
+        <v>2.687299576732522</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>429</v>
       </c>
       <c r="D4">
-        <v>0.2542808015362438</v>
+        <v>0.235275974930294</v>
       </c>
       <c r="E4">
-        <v>5.277685509079226</v>
+        <v>5.344513922649523</v>
       </c>
       <c r="F4">
-        <v>3.665107633110944</v>
+        <v>3.803208940495283</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>371</v>
       </c>
       <c r="D5">
-        <v>0.3220565964076165</v>
+        <v>0.3533086548839709</v>
       </c>
       <c r="E5">
-        <v>4.262199787542452</v>
+        <v>4.162800592841434</v>
       </c>
       <c r="F5">
-        <v>2.564476631581783</v>
+        <v>2.533091730365374</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>325</v>
       </c>
       <c r="D6">
-        <v>0.3018297021816635</v>
+        <v>0.2354224346578632</v>
       </c>
       <c r="E6">
-        <v>4.383733230825031</v>
+        <v>4.587480260062486</v>
       </c>
       <c r="F6">
-        <v>3.181054853269687</v>
+        <v>3.44435307353735</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>235</v>
       </c>
       <c r="D7">
-        <v>-0.802577158883131</v>
+        <v>-0.3123255994666378</v>
       </c>
       <c r="E7">
-        <v>5.755029407612975</v>
+        <v>4.910451384186175</v>
       </c>
       <c r="F7">
-        <v>3.661770042174674</v>
+        <v>3.381586725883027</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>223</v>
       </c>
       <c r="D8">
-        <v>0.2373845991138294</v>
+        <v>0.2843162674964222</v>
       </c>
       <c r="E8">
-        <v>4.156786691450048</v>
+        <v>4.026850682642541</v>
       </c>
       <c r="F8">
-        <v>2.945229099336761</v>
+        <v>2.704757128462129</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>84</v>
       </c>
       <c r="D9">
-        <v>0.5206258421316265</v>
+        <v>0.5217169369194814</v>
       </c>
       <c r="E9">
-        <v>5.968430989817928</v>
+        <v>5.961634801921234</v>
       </c>
       <c r="F9">
-        <v>4.630820973288445</v>
+        <v>4.173140000729334</v>
       </c>
     </row>
   </sheetData>
